--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18E58B4E-834E-4A6A-BA42-131948A96942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37407A20-B1EC-47E5-BDC6-0438820F3A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{294C434F-AB94-452A-BA56-05869EDF3E55}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{41B53D0A-5105-4B4C-9626-F4FBD4669209}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.57683391204" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{DFF6025A-60C3-4ABD-B893-EBA15BA3091F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579401504627" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{0000353F-A5CC-4BE7-9F0A-D2D5221AC773}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0005254A-550B-40E8-AE31-4191CCFB1F42}" name="AllErrorPivot" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6DD9E1A1-15FE-409A-91EA-0CE057CD1366}" name="AllErrorPivot" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -531,7 +531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3EE9230-5E67-4F34-BF3E-0CEAFFF6F8D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCDAEC7-0FF9-42E5-810E-4BC5A00C1E70}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABFE5B50-C5CD-4744-8528-DFD1D46820A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{997BE400-2D03-47BD-B9DB-5C0DC91B500D}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
